--- a/data/csvlog_schema.xlsx
+++ b/data/csvlog_schema.xlsx
@@ -87,9 +87,12 @@
     <t>Placement</t>
   </si>
   <si>
-    <t>"Hawa me,
+    <t xml:space="preserve">"Hawa me,
 At Pivot,
-At DaySupp"</t>
+At DaySupp
+Near Pivot
+Near DaySupp"
+</t>
   </si>
   <si>
     <t>Near</t>
@@ -226,7 +229,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -240,6 +243,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -292,27 +300,33 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -322,6 +336,9 @@
     </xf>
     <xf borderId="0" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +567,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -563,14 +580,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
@@ -581,14 +598,14 @@
       </c>
       <c r="F2" s="4"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+    <row r="3">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -597,18 +614,18 @@
       <c r="E3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
+    <row r="4">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
@@ -619,32 +636,32 @@
       </c>
       <c r="F4" s="4"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+    <row r="5">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
+    <row r="6">
+      <c r="A6" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -655,14 +672,14 @@
       </c>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
+    <row r="7">
+      <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -673,14 +690,14 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+    <row r="8">
+      <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -691,14 +708,14 @@
       </c>
       <c r="F8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+    <row r="9">
+      <c r="A9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -709,14 +726,14 @@
       </c>
       <c r="F9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
+    <row r="10">
+      <c r="A10" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D10" s="4" t="s">
@@ -727,14 +744,14 @@
       </c>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
+    <row r="11">
+      <c r="A11" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D11" s="4" t="s">
@@ -745,14 +762,14 @@
       </c>
       <c r="F11" s="4"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D12" s="4" t="s">
@@ -763,14 +780,14 @@
       </c>
       <c r="F12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
+    <row r="13">
+      <c r="A13" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -781,14 +798,14 @@
       </c>
       <c r="F13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+    <row r="14">
+      <c r="A14" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -799,14 +816,14 @@
       </c>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
+    <row r="15">
+      <c r="A15" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -817,14 +834,14 @@
       </c>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
+    <row r="16">
+      <c r="A16" s="7" t="s">
         <v>23</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -835,14 +852,14 @@
       </c>
       <c r="F16" s="4"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="5" t="s">
+    <row r="17">
+      <c r="A17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="5"/>
       <c r="D17" s="4" t="s">
         <v>2</v>
       </c>
@@ -851,14 +868,14 @@
       </c>
       <c r="F17" s="4"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="7" t="s">
+    <row r="18">
+      <c r="A18" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C18" s="4"/>
+      <c r="C18" s="5"/>
       <c r="D18" s="4" t="s">
         <v>42</v>
       </c>
@@ -867,14 +884,14 @@
       </c>
       <c r="F18" s="4"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="7" t="s">
+    <row r="19">
+      <c r="A19" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D19" s="4" t="s">
@@ -885,14 +902,14 @@
       </c>
       <c r="F19" s="4"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="7" t="s">
+    <row r="20">
+      <c r="A20" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -903,14 +920,14 @@
       </c>
       <c r="F20" s="4"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="7" t="s">
+    <row r="21">
+      <c r="A21" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -921,14 +938,14 @@
       </c>
       <c r="F21" s="4"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="7" t="s">
+    <row r="22">
+      <c r="A22" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -939,14 +956,14 @@
       </c>
       <c r="F22" s="4"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="7" t="s">
+    <row r="23">
+      <c r="A23" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="4" t="s">
@@ -957,14 +974,14 @@
       </c>
       <c r="F23" s="4"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="7" t="s">
+    <row r="24">
+      <c r="A24" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="4" t="s">
@@ -975,14 +992,14 @@
       </c>
       <c r="F24" s="4"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="7" t="s">
+    <row r="25">
+      <c r="A25" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="4"/>
+      <c r="C25" s="5"/>
       <c r="D25" s="4" t="s">
         <v>2</v>
       </c>
@@ -991,14 +1008,14 @@
       </c>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="7" t="s">
+    <row r="26">
+      <c r="A26" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="4"/>
+      <c r="C26" s="5"/>
       <c r="D26" s="4" t="s">
         <v>2</v>
       </c>
@@ -1007,14 +1024,14 @@
       </c>
       <c r="F26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="7" t="s">
+    <row r="27">
+      <c r="A27" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="4"/>
+      <c r="C27" s="5"/>
       <c r="D27" s="4" t="s">
         <v>2</v>
       </c>
@@ -1023,14 +1040,14 @@
       </c>
       <c r="F27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="7" t="s">
+    <row r="28">
+      <c r="A28" s="9" t="s">
         <v>40</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="4"/>
+      <c r="C28" s="5"/>
       <c r="D28" s="4" t="s">
         <v>2</v>
       </c>
@@ -1039,14 +1056,14 @@
       </c>
       <c r="F28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="8" t="s">
+    <row r="29">
+      <c r="A29" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="4"/>
+      <c r="C29" s="5"/>
       <c r="D29" s="4" t="s">
         <v>42</v>
       </c>
@@ -1055,14 +1072,14 @@
       </c>
       <c r="F29" s="4"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="8" t="s">
+    <row r="30">
+      <c r="A30" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D30" s="4" t="s">
@@ -1073,14 +1090,14 @@
       </c>
       <c r="F30" s="4"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="8" t="s">
+    <row r="31">
+      <c r="A31" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D31" s="4" t="s">
@@ -1091,14 +1108,14 @@
       </c>
       <c r="F31" s="4"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="8" t="s">
+    <row r="32">
+      <c r="A32" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="4"/>
+      <c r="C32" s="5"/>
       <c r="D32" s="4" t="s">
         <v>42</v>
       </c>
@@ -1107,14 +1124,14 @@
       </c>
       <c r="F32" s="4"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="8" t="s">
+    <row r="33">
+      <c r="A33" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D33" s="4" t="s">
@@ -1125,14 +1142,14 @@
       </c>
       <c r="F33" s="4"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="8" t="s">
+    <row r="34">
+      <c r="A34" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D34" s="4" t="s">
@@ -1143,14 +1160,14 @@
       </c>
       <c r="F34" s="4"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="8" t="s">
+    <row r="35">
+      <c r="A35" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C35" s="4"/>
+      <c r="C35" s="5"/>
       <c r="D35" s="4" t="s">
         <v>42</v>
       </c>
@@ -1159,14 +1176,14 @@
       </c>
       <c r="F35" s="4"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="8" t="s">
+    <row r="36">
+      <c r="A36" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D36" s="4" t="s">
@@ -1177,14 +1194,14 @@
       </c>
       <c r="F36" s="4"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="8" t="s">
+    <row r="37">
+      <c r="A37" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D37" s="4" t="s">
@@ -1195,14 +1212,14 @@
       </c>
       <c r="F37" s="4"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="8" t="s">
+    <row r="38">
+      <c r="A38" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C38" s="4"/>
+      <c r="C38" s="5"/>
       <c r="D38" s="4" t="s">
         <v>42</v>
       </c>
@@ -1211,14 +1228,14 @@
       </c>
       <c r="F38" s="4"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="8" t="s">
+    <row r="39">
+      <c r="A39" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D39" s="4" t="s">
@@ -1229,14 +1246,14 @@
       </c>
       <c r="F39" s="4"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="8" t="s">
+    <row r="40">
+      <c r="A40" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="6" t="s">
+      <c r="C40" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D40" s="4" t="s">
@@ -1247,14 +1264,14 @@
       </c>
       <c r="F40" s="4"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="8" t="s">
+    <row r="41">
+      <c r="A41" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="4"/>
+      <c r="C41" s="5"/>
       <c r="D41" s="4" t="s">
         <v>42</v>
       </c>
@@ -1263,14 +1280,14 @@
       </c>
       <c r="F41" s="4"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="8" t="s">
+    <row r="42">
+      <c r="A42" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="4" t="s">
@@ -1281,14 +1298,14 @@
       </c>
       <c r="F42" s="4"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="8" t="s">
+    <row r="43">
+      <c r="A43" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D43" s="4" t="s">
@@ -1302,7 +1319,7 @@
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
+      <c r="C44" s="5"/>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -1310,79 +1327,79 @@
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="11"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="11"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
+      <c r="C54" s="5"/>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
@@ -1390,7 +1407,7 @@
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
+      <c r="C55" s="5"/>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
@@ -1398,7 +1415,7 @@
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
+      <c r="C56" s="5"/>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
@@ -1406,7 +1423,7 @@
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
@@ -1414,7 +1431,7 @@
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
+      <c r="C58" s="5"/>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
@@ -1422,7 +1439,7 @@
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
+      <c r="C59" s="5"/>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -1430,7 +1447,7 @@
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
+      <c r="C60" s="5"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -1438,7 +1455,7 @@
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
+      <c r="C61" s="5"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -1446,7 +1463,7 @@
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
+      <c r="C62" s="5"/>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
@@ -1454,7 +1471,7 @@
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
+      <c r="C63" s="5"/>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
@@ -1462,7 +1479,7 @@
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
+      <c r="C64" s="5"/>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
@@ -1470,7 +1487,7 @@
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
+      <c r="C65" s="5"/>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
@@ -1478,7 +1495,7 @@
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
+      <c r="C66" s="5"/>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
@@ -1486,7 +1503,7 @@
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
+      <c r="C67" s="5"/>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
@@ -1494,7 +1511,7 @@
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
+      <c r="C68" s="5"/>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
@@ -1502,7 +1519,7 @@
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
+      <c r="C69" s="5"/>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
@@ -1510,7 +1527,7 @@
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
+      <c r="C70" s="5"/>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
@@ -1518,7 +1535,7 @@
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
+      <c r="C71" s="5"/>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
@@ -1526,7 +1543,7 @@
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
+      <c r="C72" s="5"/>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
@@ -1534,7 +1551,7 @@
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
+      <c r="C73" s="5"/>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
@@ -1542,7 +1559,7 @@
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
+      <c r="C74" s="5"/>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
@@ -1550,7 +1567,7 @@
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -1558,7 +1575,7 @@
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
+      <c r="C76" s="5"/>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
@@ -1566,7 +1583,7 @@
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
+      <c r="C77" s="5"/>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
@@ -1574,7 +1591,7 @@
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
+      <c r="C78" s="5"/>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
@@ -1582,7 +1599,7 @@
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
+      <c r="C79" s="5"/>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
@@ -1590,7 +1607,7 @@
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
-      <c r="C80" s="4"/>
+      <c r="C80" s="5"/>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
       <c r="F80" s="4"/>
@@ -1598,7 +1615,7 @@
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="4"/>
+      <c r="C81" s="5"/>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
@@ -1606,7 +1623,7 @@
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
+      <c r="C82" s="5"/>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
@@ -1614,7 +1631,7 @@
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
-      <c r="C83" s="4"/>
+      <c r="C83" s="5"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
@@ -1622,7 +1639,7 @@
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
-      <c r="C84" s="4"/>
+      <c r="C84" s="5"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="4"/>
@@ -1630,7 +1647,7 @@
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
-      <c r="C85" s="4"/>
+      <c r="C85" s="5"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
@@ -1638,7 +1655,7 @@
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
-      <c r="C86" s="4"/>
+      <c r="C86" s="5"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="4"/>
@@ -1646,7 +1663,7 @@
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
-      <c r="C87" s="4"/>
+      <c r="C87" s="5"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="4"/>
@@ -1654,7 +1671,7 @@
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
+      <c r="C88" s="5"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="4"/>
@@ -1662,7 +1679,7 @@
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
+      <c r="C89" s="5"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
@@ -1670,7 +1687,7 @@
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
+      <c r="C90" s="5"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="4"/>
@@ -1678,7 +1695,7 @@
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
+      <c r="C91" s="5"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="4"/>
@@ -1686,7 +1703,7 @@
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
+      <c r="C92" s="5"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="4"/>
@@ -1694,7 +1711,7 @@
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
+      <c r="C93" s="5"/>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
@@ -1702,7 +1719,7 @@
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
+      <c r="C94" s="5"/>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
       <c r="F94" s="4"/>
@@ -1710,7 +1727,7 @@
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
+      <c r="C95" s="5"/>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
       <c r="F95" s="4"/>
@@ -1718,7 +1735,7 @@
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
+      <c r="C96" s="5"/>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
       <c r="F96" s="4"/>
@@ -1726,7 +1743,7 @@
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
+      <c r="C97" s="5"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
@@ -1734,7 +1751,7 @@
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
+      <c r="C98" s="5"/>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
       <c r="F98" s="4"/>
@@ -1742,7 +1759,7 @@
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
+      <c r="C99" s="5"/>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
       <c r="F99" s="4"/>
@@ -1750,7 +1767,7 @@
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
+      <c r="C100" s="5"/>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
       <c r="F100" s="4"/>
@@ -1758,7 +1775,7 @@
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
+      <c r="C101" s="5"/>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
@@ -1766,7 +1783,7 @@
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
+      <c r="C102" s="5"/>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
       <c r="F102" s="4"/>
@@ -1774,7 +1791,7 @@
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
+      <c r="C103" s="5"/>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
       <c r="F103" s="4"/>
@@ -1782,7 +1799,7 @@
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
+      <c r="C104" s="5"/>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
       <c r="F104" s="4"/>
@@ -1790,7 +1807,7 @@
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
-      <c r="C105" s="4"/>
+      <c r="C105" s="5"/>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
@@ -1798,7 +1815,7 @@
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
-      <c r="C106" s="4"/>
+      <c r="C106" s="5"/>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
       <c r="F106" s="4"/>
@@ -1806,7 +1823,7 @@
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
-      <c r="C107" s="4"/>
+      <c r="C107" s="5"/>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
       <c r="F107" s="4"/>
@@ -1814,7 +1831,7 @@
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
-      <c r="C108" s="4"/>
+      <c r="C108" s="5"/>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
       <c r="F108" s="4"/>
@@ -1822,7 +1839,7 @@
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
-      <c r="C109" s="4"/>
+      <c r="C109" s="5"/>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
@@ -1830,7 +1847,7 @@
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
-      <c r="C110" s="4"/>
+      <c r="C110" s="5"/>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
       <c r="F110" s="4"/>
@@ -1838,7 +1855,7 @@
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
-      <c r="C111" s="4"/>
+      <c r="C111" s="5"/>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
       <c r="F111" s="4"/>
@@ -1846,7 +1863,7 @@
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
-      <c r="C112" s="4"/>
+      <c r="C112" s="5"/>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
       <c r="F112" s="4"/>
@@ -1854,7 +1871,7 @@
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
-      <c r="C113" s="4"/>
+      <c r="C113" s="5"/>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
@@ -1862,7 +1879,7 @@
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
-      <c r="C114" s="4"/>
+      <c r="C114" s="5"/>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
       <c r="F114" s="4"/>
@@ -1870,7 +1887,7 @@
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
-      <c r="C115" s="4"/>
+      <c r="C115" s="5"/>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
       <c r="F115" s="4"/>
@@ -1878,7 +1895,7 @@
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
-      <c r="C116" s="4"/>
+      <c r="C116" s="5"/>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
       <c r="F116" s="4"/>
@@ -1886,7 +1903,7 @@
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
-      <c r="C117" s="4"/>
+      <c r="C117" s="5"/>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
@@ -1894,7 +1911,7 @@
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
-      <c r="C118" s="4"/>
+      <c r="C118" s="5"/>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
       <c r="F118" s="4"/>
@@ -1902,7 +1919,7 @@
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
-      <c r="C119" s="4"/>
+      <c r="C119" s="5"/>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
       <c r="F119" s="4"/>
@@ -1910,7 +1927,7 @@
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
-      <c r="C120" s="4"/>
+      <c r="C120" s="5"/>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
       <c r="F120" s="4"/>
@@ -1918,7 +1935,7 @@
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
+      <c r="C121" s="5"/>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
@@ -1926,7 +1943,7 @@
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
-      <c r="C122" s="4"/>
+      <c r="C122" s="5"/>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
       <c r="F122" s="4"/>
@@ -1934,7 +1951,7 @@
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
-      <c r="C123" s="4"/>
+      <c r="C123" s="5"/>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
       <c r="F123" s="4"/>
@@ -1942,7 +1959,7 @@
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
+      <c r="C124" s="5"/>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
       <c r="F124" s="4"/>
@@ -1950,7 +1967,7 @@
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
-      <c r="C125" s="4"/>
+      <c r="C125" s="5"/>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
@@ -1958,7 +1975,7 @@
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
-      <c r="C126" s="4"/>
+      <c r="C126" s="5"/>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
       <c r="F126" s="4"/>
@@ -1966,7 +1983,7 @@
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
-      <c r="C127" s="4"/>
+      <c r="C127" s="5"/>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
       <c r="F127" s="4"/>
@@ -1974,7 +1991,7 @@
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
+      <c r="C128" s="5"/>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
       <c r="F128" s="4"/>
@@ -1982,7 +1999,7 @@
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
-      <c r="C129" s="4"/>
+      <c r="C129" s="5"/>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
@@ -1990,7 +2007,7 @@
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
-      <c r="C130" s="4"/>
+      <c r="C130" s="5"/>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
       <c r="F130" s="4"/>
@@ -1998,7 +2015,7 @@
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
-      <c r="C131" s="4"/>
+      <c r="C131" s="5"/>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
       <c r="F131" s="4"/>
@@ -2006,7 +2023,7 @@
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
-      <c r="C132" s="4"/>
+      <c r="C132" s="5"/>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
       <c r="F132" s="4"/>
@@ -2014,7 +2031,7 @@
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
+      <c r="C133" s="5"/>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
@@ -2022,7 +2039,7 @@
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
-      <c r="C134" s="4"/>
+      <c r="C134" s="5"/>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
       <c r="F134" s="4"/>
@@ -2030,7 +2047,7 @@
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
-      <c r="C135" s="4"/>
+      <c r="C135" s="5"/>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
       <c r="F135" s="4"/>
@@ -2038,7 +2055,7 @@
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
+      <c r="C136" s="5"/>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
       <c r="F136" s="4"/>
@@ -2046,7 +2063,7 @@
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
+      <c r="C137" s="5"/>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
@@ -2054,7 +2071,7 @@
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
+      <c r="C138" s="5"/>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
       <c r="F138" s="4"/>
@@ -2062,7 +2079,7 @@
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
+      <c r="C139" s="5"/>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
       <c r="F139" s="4"/>
@@ -2070,7 +2087,7 @@
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
+      <c r="C140" s="5"/>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
       <c r="F140" s="4"/>
@@ -2078,7 +2095,7 @@
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
+      <c r="C141" s="5"/>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
@@ -2086,7 +2103,7 @@
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
+      <c r="C142" s="5"/>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
       <c r="F142" s="4"/>
@@ -2094,7 +2111,7 @@
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
+      <c r="C143" s="5"/>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
       <c r="F143" s="4"/>
@@ -2102,7 +2119,7 @@
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
+      <c r="C144" s="5"/>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
       <c r="F144" s="4"/>
@@ -2110,7 +2127,7 @@
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
+      <c r="C145" s="5"/>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
@@ -2118,7 +2135,7 @@
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
+      <c r="C146" s="5"/>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
       <c r="F146" s="4"/>
@@ -2126,7 +2143,7 @@
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
+      <c r="C147" s="5"/>
       <c r="D147" s="4"/>
       <c r="E147" s="4"/>
       <c r="F147" s="4"/>
@@ -2134,7 +2151,7 @@
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
+      <c r="C148" s="5"/>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
       <c r="F148" s="4"/>
@@ -2142,7 +2159,7 @@
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
-      <c r="C149" s="4"/>
+      <c r="C149" s="5"/>
       <c r="D149" s="4"/>
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
@@ -2150,7 +2167,7 @@
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
-      <c r="C150" s="4"/>
+      <c r="C150" s="5"/>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
       <c r="F150" s="4"/>
@@ -2158,7 +2175,7 @@
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
-      <c r="C151" s="4"/>
+      <c r="C151" s="5"/>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
       <c r="F151" s="4"/>
@@ -2166,7 +2183,7 @@
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
-      <c r="C152" s="4"/>
+      <c r="C152" s="5"/>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
       <c r="F152" s="4"/>
@@ -2174,7 +2191,7 @@
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
+      <c r="C153" s="5"/>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
@@ -2182,7 +2199,7 @@
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
-      <c r="C154" s="4"/>
+      <c r="C154" s="5"/>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
       <c r="F154" s="4"/>
@@ -2190,7 +2207,7 @@
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
-      <c r="C155" s="4"/>
+      <c r="C155" s="5"/>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
       <c r="F155" s="4"/>
@@ -2198,7 +2215,7 @@
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
-      <c r="C156" s="4"/>
+      <c r="C156" s="5"/>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
       <c r="F156" s="4"/>
@@ -2206,7 +2223,7 @@
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
-      <c r="C157" s="4"/>
+      <c r="C157" s="5"/>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
@@ -2214,7 +2231,7 @@
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
-      <c r="C158" s="4"/>
+      <c r="C158" s="5"/>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
       <c r="F158" s="4"/>
@@ -2222,7 +2239,7 @@
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
+      <c r="C159" s="5"/>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
       <c r="F159" s="4"/>
@@ -2230,7 +2247,7 @@
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
+      <c r="C160" s="5"/>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
       <c r="F160" s="4"/>
@@ -2238,7 +2255,7 @@
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
-      <c r="C161" s="4"/>
+      <c r="C161" s="5"/>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
@@ -2246,7 +2263,7 @@
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
-      <c r="C162" s="4"/>
+      <c r="C162" s="5"/>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
       <c r="F162" s="4"/>
@@ -2254,7 +2271,7 @@
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
+      <c r="C163" s="5"/>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
       <c r="F163" s="4"/>
@@ -2262,7 +2279,7 @@
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
-      <c r="C164" s="4"/>
+      <c r="C164" s="5"/>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
       <c r="F164" s="4"/>
@@ -2270,7 +2287,7 @@
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
-      <c r="C165" s="4"/>
+      <c r="C165" s="5"/>
       <c r="D165" s="4"/>
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
@@ -2278,7 +2295,7 @@
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
-      <c r="C166" s="4"/>
+      <c r="C166" s="5"/>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
       <c r="F166" s="4"/>
@@ -2286,7 +2303,7 @@
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
+      <c r="C167" s="5"/>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
       <c r="F167" s="4"/>
@@ -2294,7 +2311,7 @@
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
+      <c r="C168" s="5"/>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
       <c r="F168" s="4"/>
@@ -2302,7 +2319,7 @@
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
-      <c r="C169" s="4"/>
+      <c r="C169" s="5"/>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
@@ -2310,7 +2327,7 @@
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
-      <c r="C170" s="4"/>
+      <c r="C170" s="5"/>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
       <c r="F170" s="4"/>
@@ -2318,7 +2335,7 @@
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
-      <c r="C171" s="4"/>
+      <c r="C171" s="5"/>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
       <c r="F171" s="4"/>
@@ -2326,7 +2343,7 @@
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
-      <c r="C172" s="4"/>
+      <c r="C172" s="5"/>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
       <c r="F172" s="4"/>
@@ -2334,7 +2351,7 @@
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
+      <c r="C173" s="5"/>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
@@ -2342,7 +2359,7 @@
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
+      <c r="C174" s="5"/>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
       <c r="F174" s="4"/>
@@ -2350,7 +2367,7 @@
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
-      <c r="C175" s="4"/>
+      <c r="C175" s="5"/>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
       <c r="F175" s="4"/>
@@ -2358,7 +2375,7 @@
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
-      <c r="C176" s="4"/>
+      <c r="C176" s="5"/>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
       <c r="F176" s="4"/>
@@ -2366,7 +2383,7 @@
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
-      <c r="C177" s="4"/>
+      <c r="C177" s="5"/>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
@@ -2374,7 +2391,7 @@
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
+      <c r="C178" s="5"/>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
       <c r="F178" s="4"/>
@@ -2382,7 +2399,7 @@
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
-      <c r="C179" s="4"/>
+      <c r="C179" s="5"/>
       <c r="D179" s="4"/>
       <c r="E179" s="4"/>
       <c r="F179" s="4"/>
@@ -2390,7 +2407,7 @@
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
+      <c r="C180" s="5"/>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
       <c r="F180" s="4"/>
@@ -2398,7 +2415,7 @@
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
-      <c r="C181" s="4"/>
+      <c r="C181" s="5"/>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
@@ -2406,7 +2423,7 @@
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
+      <c r="C182" s="5"/>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
       <c r="F182" s="4"/>
@@ -2414,7 +2431,7 @@
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
-      <c r="C183" s="4"/>
+      <c r="C183" s="5"/>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
       <c r="F183" s="4"/>
@@ -2422,7 +2439,7 @@
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
-      <c r="C184" s="4"/>
+      <c r="C184" s="5"/>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
       <c r="F184" s="4"/>
@@ -2430,7 +2447,7 @@
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
+      <c r="C185" s="5"/>
       <c r="D185" s="4"/>
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
@@ -2438,7 +2455,7 @@
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
-      <c r="C186" s="4"/>
+      <c r="C186" s="5"/>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
       <c r="F186" s="4"/>
@@ -2446,7 +2463,7 @@
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
+      <c r="C187" s="5"/>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
       <c r="F187" s="4"/>
@@ -2454,7 +2471,7 @@
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
-      <c r="C188" s="4"/>
+      <c r="C188" s="5"/>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
       <c r="F188" s="4"/>
@@ -2462,7 +2479,7 @@
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
-      <c r="C189" s="4"/>
+      <c r="C189" s="5"/>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
@@ -2470,7 +2487,7 @@
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
-      <c r="C190" s="4"/>
+      <c r="C190" s="5"/>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
       <c r="F190" s="4"/>
@@ -2478,7 +2495,7 @@
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
+      <c r="C191" s="5"/>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
       <c r="F191" s="4"/>
@@ -2486,7 +2503,7 @@
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
-      <c r="C192" s="4"/>
+      <c r="C192" s="5"/>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
       <c r="F192" s="4"/>
@@ -2494,7 +2511,7 @@
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
-      <c r="C193" s="4"/>
+      <c r="C193" s="5"/>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
@@ -2502,7 +2519,7 @@
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
-      <c r="C194" s="4"/>
+      <c r="C194" s="5"/>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
       <c r="F194" s="4"/>
@@ -2510,7 +2527,7 @@
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
-      <c r="C195" s="4"/>
+      <c r="C195" s="5"/>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
       <c r="F195" s="4"/>
@@ -2518,7 +2535,7 @@
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
-      <c r="C196" s="4"/>
+      <c r="C196" s="5"/>
       <c r="D196" s="4"/>
       <c r="E196" s="4"/>
       <c r="F196" s="4"/>
@@ -2526,7 +2543,7 @@
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
+      <c r="C197" s="5"/>
       <c r="D197" s="4"/>
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
@@ -2534,7 +2551,7 @@
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
-      <c r="C198" s="4"/>
+      <c r="C198" s="5"/>
       <c r="D198" s="4"/>
       <c r="E198" s="4"/>
       <c r="F198" s="4"/>
@@ -2542,7 +2559,7 @@
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
-      <c r="C199" s="4"/>
+      <c r="C199" s="5"/>
       <c r="D199" s="4"/>
       <c r="E199" s="4"/>
       <c r="F199" s="4"/>
@@ -2550,7 +2567,7 @@
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
+      <c r="C200" s="5"/>
       <c r="D200" s="4"/>
       <c r="E200" s="4"/>
       <c r="F200" s="4"/>
@@ -2558,7 +2575,7 @@
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
-      <c r="C201" s="4"/>
+      <c r="C201" s="5"/>
       <c r="D201" s="4"/>
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
@@ -2566,7 +2583,7 @@
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
-      <c r="C202" s="4"/>
+      <c r="C202" s="5"/>
       <c r="D202" s="4"/>
       <c r="E202" s="4"/>
       <c r="F202" s="4"/>
@@ -2574,7 +2591,7 @@
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
-      <c r="C203" s="4"/>
+      <c r="C203" s="5"/>
       <c r="D203" s="4"/>
       <c r="E203" s="4"/>
       <c r="F203" s="4"/>
@@ -2582,7 +2599,7 @@
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
+      <c r="C204" s="5"/>
       <c r="D204" s="4"/>
       <c r="E204" s="4"/>
       <c r="F204" s="4"/>
@@ -2590,7 +2607,7 @@
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
-      <c r="C205" s="4"/>
+      <c r="C205" s="5"/>
       <c r="D205" s="4"/>
       <c r="E205" s="4"/>
       <c r="F205" s="4"/>
@@ -2598,7 +2615,7 @@
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
+      <c r="C206" s="5"/>
       <c r="D206" s="4"/>
       <c r="E206" s="4"/>
       <c r="F206" s="4"/>
@@ -2606,7 +2623,7 @@
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
-      <c r="C207" s="4"/>
+      <c r="C207" s="5"/>
       <c r="D207" s="4"/>
       <c r="E207" s="4"/>
       <c r="F207" s="4"/>
@@ -2614,7 +2631,7 @@
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
-      <c r="C208" s="4"/>
+      <c r="C208" s="5"/>
       <c r="D208" s="4"/>
       <c r="E208" s="4"/>
       <c r="F208" s="4"/>
@@ -2622,7 +2639,7 @@
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
+      <c r="C209" s="5"/>
       <c r="D209" s="4"/>
       <c r="E209" s="4"/>
       <c r="F209" s="4"/>
@@ -2630,7 +2647,7 @@
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
-      <c r="C210" s="4"/>
+      <c r="C210" s="5"/>
       <c r="D210" s="4"/>
       <c r="E210" s="4"/>
       <c r="F210" s="4"/>
@@ -2638,7 +2655,7 @@
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
-      <c r="C211" s="4"/>
+      <c r="C211" s="5"/>
       <c r="D211" s="4"/>
       <c r="E211" s="4"/>
       <c r="F211" s="4"/>
@@ -2646,7 +2663,7 @@
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
-      <c r="C212" s="4"/>
+      <c r="C212" s="5"/>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
       <c r="F212" s="4"/>
@@ -2654,7 +2671,7 @@
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
+      <c r="C213" s="5"/>
       <c r="D213" s="4"/>
       <c r="E213" s="4"/>
       <c r="F213" s="4"/>
@@ -2662,7 +2679,7 @@
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
-      <c r="C214" s="4"/>
+      <c r="C214" s="5"/>
       <c r="D214" s="4"/>
       <c r="E214" s="4"/>
       <c r="F214" s="4"/>
@@ -2670,7 +2687,7 @@
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
-      <c r="C215" s="4"/>
+      <c r="C215" s="5"/>
       <c r="D215" s="4"/>
       <c r="E215" s="4"/>
       <c r="F215" s="4"/>
@@ -2678,7 +2695,7 @@
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
+      <c r="C216" s="5"/>
       <c r="D216" s="4"/>
       <c r="E216" s="4"/>
       <c r="F216" s="4"/>
@@ -2686,7 +2703,7 @@
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
-      <c r="C217" s="4"/>
+      <c r="C217" s="5"/>
       <c r="D217" s="4"/>
       <c r="E217" s="4"/>
       <c r="F217" s="4"/>
@@ -2694,7 +2711,7 @@
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
-      <c r="C218" s="4"/>
+      <c r="C218" s="5"/>
       <c r="D218" s="4"/>
       <c r="E218" s="4"/>
       <c r="F218" s="4"/>
@@ -2702,7 +2719,7 @@
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
-      <c r="C219" s="4"/>
+      <c r="C219" s="5"/>
       <c r="D219" s="4"/>
       <c r="E219" s="4"/>
       <c r="F219" s="4"/>
@@ -2710,7 +2727,7 @@
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
+      <c r="C220" s="5"/>
       <c r="D220" s="4"/>
       <c r="E220" s="4"/>
       <c r="F220" s="4"/>
@@ -2718,7 +2735,7 @@
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="4"/>
       <c r="B221" s="4"/>
-      <c r="C221" s="4"/>
+      <c r="C221" s="5"/>
       <c r="D221" s="4"/>
       <c r="E221" s="4"/>
       <c r="F221" s="4"/>
@@ -2726,7 +2743,7 @@
     <row r="222" ht="15.75" customHeight="1">
       <c r="A222" s="4"/>
       <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
+      <c r="C222" s="5"/>
       <c r="D222" s="4"/>
       <c r="E222" s="4"/>
       <c r="F222" s="4"/>
@@ -2734,7 +2751,7 @@
     <row r="223" ht="15.75" customHeight="1">
       <c r="A223" s="4"/>
       <c r="B223" s="4"/>
-      <c r="C223" s="4"/>
+      <c r="C223" s="5"/>
       <c r="D223" s="4"/>
       <c r="E223" s="4"/>
       <c r="F223" s="4"/>
@@ -2742,7 +2759,7 @@
     <row r="224" ht="15.75" customHeight="1">
       <c r="A224" s="4"/>
       <c r="B224" s="4"/>
-      <c r="C224" s="4"/>
+      <c r="C224" s="5"/>
       <c r="D224" s="4"/>
       <c r="E224" s="4"/>
       <c r="F224" s="4"/>
@@ -2750,7 +2767,7 @@
     <row r="225" ht="15.75" customHeight="1">
       <c r="A225" s="4"/>
       <c r="B225" s="4"/>
-      <c r="C225" s="4"/>
+      <c r="C225" s="5"/>
       <c r="D225" s="4"/>
       <c r="E225" s="4"/>
       <c r="F225" s="4"/>
@@ -2758,7 +2775,7 @@
     <row r="226" ht="15.75" customHeight="1">
       <c r="A226" s="4"/>
       <c r="B226" s="4"/>
-      <c r="C226" s="4"/>
+      <c r="C226" s="5"/>
       <c r="D226" s="4"/>
       <c r="E226" s="4"/>
       <c r="F226" s="4"/>
@@ -2766,7 +2783,7 @@
     <row r="227" ht="15.75" customHeight="1">
       <c r="A227" s="4"/>
       <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
+      <c r="C227" s="5"/>
       <c r="D227" s="4"/>
       <c r="E227" s="4"/>
       <c r="F227" s="4"/>
@@ -2774,7 +2791,7 @@
     <row r="228" ht="15.75" customHeight="1">
       <c r="A228" s="4"/>
       <c r="B228" s="4"/>
-      <c r="C228" s="4"/>
+      <c r="C228" s="5"/>
       <c r="D228" s="4"/>
       <c r="E228" s="4"/>
       <c r="F228" s="4"/>
@@ -2782,7 +2799,7 @@
     <row r="229" ht="15.75" customHeight="1">
       <c r="A229" s="4"/>
       <c r="B229" s="4"/>
-      <c r="C229" s="4"/>
+      <c r="C229" s="5"/>
       <c r="D229" s="4"/>
       <c r="E229" s="4"/>
       <c r="F229" s="4"/>
@@ -2790,7 +2807,7 @@
     <row r="230" ht="15.75" customHeight="1">
       <c r="A230" s="4"/>
       <c r="B230" s="4"/>
-      <c r="C230" s="4"/>
+      <c r="C230" s="5"/>
       <c r="D230" s="4"/>
       <c r="E230" s="4"/>
       <c r="F230" s="4"/>
@@ -2798,7 +2815,7 @@
     <row r="231" ht="15.75" customHeight="1">
       <c r="A231" s="4"/>
       <c r="B231" s="4"/>
-      <c r="C231" s="4"/>
+      <c r="C231" s="5"/>
       <c r="D231" s="4"/>
       <c r="E231" s="4"/>
       <c r="F231" s="4"/>
@@ -2806,7 +2823,7 @@
     <row r="232" ht="15.75" customHeight="1">
       <c r="A232" s="4"/>
       <c r="B232" s="4"/>
-      <c r="C232" s="4"/>
+      <c r="C232" s="5"/>
       <c r="D232" s="4"/>
       <c r="E232" s="4"/>
       <c r="F232" s="4"/>
@@ -2814,7 +2831,7 @@
     <row r="233" ht="15.75" customHeight="1">
       <c r="A233" s="4"/>
       <c r="B233" s="4"/>
-      <c r="C233" s="4"/>
+      <c r="C233" s="5"/>
       <c r="D233" s="4"/>
       <c r="E233" s="4"/>
       <c r="F233" s="4"/>
@@ -2822,7 +2839,7 @@
     <row r="234" ht="15.75" customHeight="1">
       <c r="A234" s="4"/>
       <c r="B234" s="4"/>
-      <c r="C234" s="4"/>
+      <c r="C234" s="5"/>
       <c r="D234" s="4"/>
       <c r="E234" s="4"/>
       <c r="F234" s="4"/>
@@ -2830,7 +2847,7 @@
     <row r="235" ht="15.75" customHeight="1">
       <c r="A235" s="4"/>
       <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
+      <c r="C235" s="5"/>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
       <c r="F235" s="4"/>
@@ -2838,7 +2855,7 @@
     <row r="236" ht="15.75" customHeight="1">
       <c r="A236" s="4"/>
       <c r="B236" s="4"/>
-      <c r="C236" s="4"/>
+      <c r="C236" s="5"/>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
       <c r="F236" s="4"/>
@@ -2846,7 +2863,7 @@
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="4"/>
       <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
+      <c r="C237" s="5"/>
       <c r="D237" s="4"/>
       <c r="E237" s="4"/>
       <c r="F237" s="4"/>
@@ -2854,7 +2871,7 @@
     <row r="238" ht="15.75" customHeight="1">
       <c r="A238" s="4"/>
       <c r="B238" s="4"/>
-      <c r="C238" s="4"/>
+      <c r="C238" s="5"/>
       <c r="D238" s="4"/>
       <c r="E238" s="4"/>
       <c r="F238" s="4"/>
@@ -2862,7 +2879,7 @@
     <row r="239" ht="15.75" customHeight="1">
       <c r="A239" s="4"/>
       <c r="B239" s="4"/>
-      <c r="C239" s="4"/>
+      <c r="C239" s="5"/>
       <c r="D239" s="4"/>
       <c r="E239" s="4"/>
       <c r="F239" s="4"/>
@@ -2870,7 +2887,7 @@
     <row r="240" ht="15.75" customHeight="1">
       <c r="A240" s="4"/>
       <c r="B240" s="4"/>
-      <c r="C240" s="4"/>
+      <c r="C240" s="5"/>
       <c r="D240" s="4"/>
       <c r="E240" s="4"/>
       <c r="F240" s="4"/>
@@ -2878,7 +2895,7 @@
     <row r="241" ht="15.75" customHeight="1">
       <c r="A241" s="4"/>
       <c r="B241" s="4"/>
-      <c r="C241" s="4"/>
+      <c r="C241" s="5"/>
       <c r="D241" s="4"/>
       <c r="E241" s="4"/>
       <c r="F241" s="4"/>
@@ -2886,7 +2903,7 @@
     <row r="242" ht="15.75" customHeight="1">
       <c r="A242" s="4"/>
       <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
+      <c r="C242" s="5"/>
       <c r="D242" s="4"/>
       <c r="E242" s="4"/>
       <c r="F242" s="4"/>
@@ -2894,770 +2911,2282 @@
     <row r="243" ht="15.75" customHeight="1">
       <c r="A243" s="4"/>
       <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
+      <c r="C243" s="5"/>
       <c r="D243" s="4"/>
       <c r="E243" s="4"/>
       <c r="F243" s="4"/>
     </row>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="C244" s="12"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="C245" s="12"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="C246" s="12"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="C247" s="12"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="C248" s="12"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="C249" s="12"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="C250" s="12"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="C251" s="12"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="C252" s="12"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="C253" s="12"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="C254" s="12"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="C255" s="12"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="C256" s="12"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="C257" s="12"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="C258" s="12"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="C259" s="12"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="C260" s="12"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="C261" s="12"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="C262" s="12"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="C263" s="12"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="C264" s="12"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="C265" s="12"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="C266" s="12"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="C267" s="12"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="C268" s="12"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="C269" s="12"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="C270" s="12"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="C271" s="12"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="C272" s="12"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="C273" s="12"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="C274" s="12"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="C275" s="12"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="C276" s="12"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="C277" s="12"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="C278" s="12"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="C279" s="12"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="C280" s="12"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="C281" s="12"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="C282" s="12"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="C283" s="12"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="C284" s="12"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="C285" s="12"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="C286" s="12"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="C287" s="12"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="C288" s="12"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="C289" s="12"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="C290" s="12"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="C291" s="12"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="C292" s="12"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="C293" s="12"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="C294" s="12"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="C295" s="12"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="C296" s="12"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="C297" s="12"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="C298" s="12"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="C299" s="12"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="C300" s="12"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="C301" s="12"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="C302" s="12"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="C303" s="12"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="C304" s="12"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="C305" s="12"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="C306" s="12"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="C307" s="12"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="C308" s="12"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="C309" s="12"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="C310" s="12"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="C311" s="12"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="C312" s="12"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="C313" s="12"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="C314" s="12"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="C315" s="12"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="C316" s="12"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="C317" s="12"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="C318" s="12"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="C319" s="12"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="C320" s="12"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="C321" s="12"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="C322" s="12"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="C323" s="12"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="C324" s="12"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="C325" s="12"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="C326" s="12"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="C327" s="12"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="C328" s="12"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="C329" s="12"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="C330" s="12"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="C331" s="12"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="C332" s="12"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="C333" s="12"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="C334" s="12"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="C335" s="12"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="C336" s="12"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="C337" s="12"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="C338" s="12"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="C339" s="12"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="C340" s="12"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="C341" s="12"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="C342" s="12"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="C343" s="12"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="C344" s="12"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="C345" s="12"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="C346" s="12"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="C347" s="12"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="C348" s="12"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="C349" s="12"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="C350" s="12"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="C351" s="12"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="C352" s="12"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="C353" s="12"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="C354" s="12"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="C355" s="12"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="C356" s="12"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="C357" s="12"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="C358" s="12"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="C359" s="12"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="C360" s="12"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="C361" s="12"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="C362" s="12"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="C363" s="12"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="C364" s="12"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="C365" s="12"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="C366" s="12"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="C367" s="12"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="C368" s="12"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="C369" s="12"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="C370" s="12"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="C371" s="12"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="C372" s="12"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="C373" s="12"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="C374" s="12"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="C375" s="12"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="C376" s="12"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="C377" s="12"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="C378" s="12"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="C379" s="12"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="C380" s="12"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="C381" s="12"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="C382" s="12"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="C383" s="12"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="C384" s="12"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="C385" s="12"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="C386" s="12"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="C387" s="12"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="C388" s="12"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="C389" s="12"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="C390" s="12"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="C391" s="12"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="C392" s="12"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="C393" s="12"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="C394" s="12"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="C395" s="12"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="C396" s="12"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="C397" s="12"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="C398" s="12"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="C399" s="12"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="C400" s="12"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="C401" s="12"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="C402" s="12"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="C403" s="12"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="C404" s="12"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="C405" s="12"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="C406" s="12"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="C407" s="12"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="C408" s="12"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="C409" s="12"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="C410" s="12"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="C411" s="12"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="C412" s="12"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="C413" s="12"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="C414" s="12"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="C415" s="12"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="C416" s="12"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="C417" s="12"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="C418" s="12"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="C419" s="12"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="C420" s="12"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="C421" s="12"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="C422" s="12"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="C423" s="12"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="C424" s="12"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="C425" s="12"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="C426" s="12"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="C427" s="12"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="C428" s="12"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="C429" s="12"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="C430" s="12"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="C431" s="12"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="C432" s="12"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="C433" s="12"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="C434" s="12"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="C435" s="12"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="C436" s="12"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="C437" s="12"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="C438" s="12"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="C439" s="12"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="C440" s="12"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="C441" s="12"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="C442" s="12"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="C443" s="12"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="C444" s="12"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="C445" s="12"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="C446" s="12"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="C447" s="12"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="C448" s="12"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="C449" s="12"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="C450" s="12"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="C451" s="12"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="C452" s="12"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="C453" s="12"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="C454" s="12"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="C455" s="12"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="C456" s="12"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="C457" s="12"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="C458" s="12"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="C459" s="12"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="C460" s="12"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="C461" s="12"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="C462" s="12"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="C463" s="12"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="C464" s="12"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="C465" s="12"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="C466" s="12"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="C467" s="12"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="C468" s="12"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="C469" s="12"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="C470" s="12"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="C471" s="12"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="C472" s="12"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="C473" s="12"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="C474" s="12"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="C475" s="12"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="C476" s="12"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="C477" s="12"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="C478" s="12"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="C479" s="12"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="C480" s="12"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="C481" s="12"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="C482" s="12"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="C483" s="12"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="C484" s="12"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="C485" s="12"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="C486" s="12"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="C487" s="12"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="C488" s="12"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="C489" s="12"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="C490" s="12"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="C491" s="12"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="C492" s="12"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="C493" s="12"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="C494" s="12"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="C495" s="12"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="C496" s="12"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="C497" s="12"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="C498" s="12"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="C499" s="12"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="C500" s="12"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="C501" s="12"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="C502" s="12"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="C503" s="12"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="C504" s="12"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="C505" s="12"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="C506" s="12"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="C507" s="12"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="C508" s="12"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="C509" s="12"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="C510" s="12"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="C511" s="12"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="C512" s="12"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="C513" s="12"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="C514" s="12"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="C515" s="12"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="C516" s="12"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="C517" s="12"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="C518" s="12"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="C519" s="12"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="C520" s="12"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="C521" s="12"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="C522" s="12"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="C523" s="12"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="C524" s="12"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="C525" s="12"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="C526" s="12"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="C527" s="12"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="C528" s="12"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="C529" s="12"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="C530" s="12"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="C531" s="12"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="C532" s="12"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="C533" s="12"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="C534" s="12"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="C535" s="12"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="C536" s="12"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="C537" s="12"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="C538" s="12"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="C539" s="12"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="C540" s="12"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="C541" s="12"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="C542" s="12"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="C543" s="12"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="C544" s="12"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="C545" s="12"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="C546" s="12"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="C547" s="12"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="C548" s="12"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="C549" s="12"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="C550" s="12"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="C551" s="12"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="C552" s="12"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="C553" s="12"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="C554" s="12"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="C555" s="12"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="C556" s="12"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="C557" s="12"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="C558" s="12"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="C559" s="12"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="C560" s="12"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="C561" s="12"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="C562" s="12"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="C563" s="12"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="C564" s="12"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="C565" s="12"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="C566" s="12"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="C567" s="12"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="C568" s="12"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="C569" s="12"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="C570" s="12"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="C571" s="12"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="C572" s="12"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="C573" s="12"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="C574" s="12"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="C575" s="12"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="C576" s="12"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="C577" s="12"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="C578" s="12"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="C579" s="12"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="C580" s="12"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="C581" s="12"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="C582" s="12"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="C583" s="12"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="C584" s="12"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="C585" s="12"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="C586" s="12"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="C587" s="12"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="C588" s="12"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="C589" s="12"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="C590" s="12"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="C591" s="12"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="C592" s="12"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="C593" s="12"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="C594" s="12"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="C595" s="12"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="C596" s="12"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="C597" s="12"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="C598" s="12"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="C599" s="12"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="C600" s="12"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="C601" s="12"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="C602" s="12"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="C603" s="12"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="C604" s="12"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="C605" s="12"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="C606" s="12"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="C607" s="12"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="C608" s="12"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="C609" s="12"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="C610" s="12"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="C611" s="12"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="C612" s="12"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="C613" s="12"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="C614" s="12"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="C615" s="12"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="C616" s="12"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="C617" s="12"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="C618" s="12"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="C619" s="12"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="C620" s="12"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="C621" s="12"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="C622" s="12"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="C623" s="12"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="C624" s="12"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="C625" s="12"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="C626" s="12"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="C627" s="12"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="C628" s="12"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="C629" s="12"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="C630" s="12"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="C631" s="12"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="C632" s="12"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="C633" s="12"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="C634" s="12"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="C635" s="12"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="C636" s="12"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="C637" s="12"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="C638" s="12"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="C639" s="12"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="C640" s="12"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="C641" s="12"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="C642" s="12"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="C643" s="12"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="C644" s="12"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="C645" s="12"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="C646" s="12"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="C647" s="12"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="C648" s="12"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="C649" s="12"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="C650" s="12"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="C651" s="12"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="C652" s="12"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="C653" s="12"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="C654" s="12"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="C655" s="12"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="C656" s="12"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="C657" s="12"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="C658" s="12"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="C659" s="12"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="C660" s="12"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="C661" s="12"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="C662" s="12"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="C663" s="12"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="C664" s="12"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="C665" s="12"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="C666" s="12"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="C667" s="12"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="C668" s="12"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="C669" s="12"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="C670" s="12"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="C671" s="12"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="C672" s="12"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="C673" s="12"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="C674" s="12"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="C675" s="12"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="C676" s="12"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="C677" s="12"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="C678" s="12"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="C679" s="12"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="C680" s="12"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="C681" s="12"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="C682" s="12"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="C683" s="12"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="C684" s="12"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="C685" s="12"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="C686" s="12"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="C687" s="12"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="C688" s="12"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="C689" s="12"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="C690" s="12"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="C691" s="12"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="C692" s="12"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="C693" s="12"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="C694" s="12"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="C695" s="12"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="C696" s="12"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="C697" s="12"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="C698" s="12"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="C699" s="12"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="C700" s="12"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="C701" s="12"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="C702" s="12"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="C703" s="12"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="C704" s="12"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="C705" s="12"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="C706" s="12"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="C707" s="12"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="C708" s="12"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="C709" s="12"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="C710" s="12"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="C711" s="12"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="C712" s="12"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="C713" s="12"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="C714" s="12"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="C715" s="12"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="C716" s="12"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="C717" s="12"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="C718" s="12"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="C719" s="12"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="C720" s="12"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="C721" s="12"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="C722" s="12"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="C723" s="12"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="C724" s="12"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="C725" s="12"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="C726" s="12"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="C727" s="12"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="C728" s="12"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="C729" s="12"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="C730" s="12"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="C731" s="12"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="C732" s="12"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="C733" s="12"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="C734" s="12"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="C735" s="12"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="C736" s="12"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="C737" s="12"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="C738" s="12"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="C739" s="12"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="C740" s="12"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="C741" s="12"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="C742" s="12"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="C743" s="12"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="C744" s="12"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="C745" s="12"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="C746" s="12"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="C747" s="12"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="C748" s="12"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="C749" s="12"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="C750" s="12"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="C751" s="12"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="C752" s="12"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="C753" s="12"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="C754" s="12"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="C755" s="12"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="C756" s="12"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="C757" s="12"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="C758" s="12"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="C759" s="12"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="C760" s="12"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="C761" s="12"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="C762" s="12"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="C763" s="12"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="C764" s="12"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="C765" s="12"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="C766" s="12"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="C767" s="12"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="C768" s="12"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="C769" s="12"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="C770" s="12"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="C771" s="12"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="C772" s="12"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="C773" s="12"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="C774" s="12"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="C775" s="12"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="C776" s="12"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="C777" s="12"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="C778" s="12"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="C779" s="12"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="C780" s="12"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="C781" s="12"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="C782" s="12"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="C783" s="12"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="C784" s="12"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="C785" s="12"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="C786" s="12"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="C787" s="12"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="C788" s="12"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="C789" s="12"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="C790" s="12"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="C791" s="12"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="C792" s="12"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="C793" s="12"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="C794" s="12"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="C795" s="12"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="C796" s="12"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="C797" s="12"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="C798" s="12"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="C799" s="12"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="C800" s="12"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="C801" s="12"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="C802" s="12"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="C803" s="12"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="C804" s="12"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="C805" s="12"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="C806" s="12"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="C807" s="12"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="C808" s="12"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="C809" s="12"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="C810" s="12"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="C811" s="12"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="C812" s="12"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="C813" s="12"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="C814" s="12"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="C815" s="12"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="C816" s="12"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="C817" s="12"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="C818" s="12"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="C819" s="12"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="C820" s="12"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="C821" s="12"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="C822" s="12"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="C823" s="12"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="C824" s="12"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="C825" s="12"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="C826" s="12"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="C827" s="12"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="C828" s="12"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="C829" s="12"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="C830" s="12"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="C831" s="12"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="C832" s="12"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="C833" s="12"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="C834" s="12"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="C835" s="12"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="C836" s="12"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="C837" s="12"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="C838" s="12"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="C839" s="12"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="C840" s="12"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="C841" s="12"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="C842" s="12"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="C843" s="12"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="C844" s="12"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="C845" s="12"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="C846" s="12"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="C847" s="12"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="C848" s="12"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="C849" s="12"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="C850" s="12"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="C851" s="12"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="C852" s="12"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="C853" s="12"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="C854" s="12"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="C855" s="12"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="C856" s="12"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="C857" s="12"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="C858" s="12"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="C859" s="12"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="C860" s="12"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="C861" s="12"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="C862" s="12"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="C863" s="12"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="C864" s="12"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="C865" s="12"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="C866" s="12"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="C867" s="12"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="C868" s="12"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="C869" s="12"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="C870" s="12"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="C871" s="12"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="C872" s="12"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="C873" s="12"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="C874" s="12"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="C875" s="12"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="C876" s="12"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="C877" s="12"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="C878" s="12"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="C879" s="12"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="C880" s="12"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="C881" s="12"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="C882" s="12"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="C883" s="12"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="C884" s="12"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="C885" s="12"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="C886" s="12"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="C887" s="12"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="C888" s="12"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="C889" s="12"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="C890" s="12"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="C891" s="12"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="C892" s="12"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="C893" s="12"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="C894" s="12"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="C895" s="12"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="C896" s="12"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="C897" s="12"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="C898" s="12"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="C899" s="12"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="C900" s="12"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="C901" s="12"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="C902" s="12"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="C903" s="12"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="C904" s="12"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="C905" s="12"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="C906" s="12"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="C907" s="12"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="C908" s="12"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="C909" s="12"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="C910" s="12"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="C911" s="12"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="C912" s="12"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="C913" s="12"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="C914" s="12"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="C915" s="12"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="C916" s="12"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="C917" s="12"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="C918" s="12"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="C919" s="12"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="C920" s="12"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="C921" s="12"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="C922" s="12"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="C923" s="12"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="C924" s="12"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="C925" s="12"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="C926" s="12"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="C927" s="12"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="C928" s="12"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="C929" s="12"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="C930" s="12"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="C931" s="12"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="C932" s="12"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="C933" s="12"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="C934" s="12"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="C935" s="12"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="C936" s="12"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="C937" s="12"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="C938" s="12"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="C939" s="12"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="C940" s="12"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="C941" s="12"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="C942" s="12"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="C943" s="12"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="C944" s="12"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="C945" s="12"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="C946" s="12"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="C947" s="12"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="C948" s="12"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="C949" s="12"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="C950" s="12"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="C951" s="12"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="C952" s="12"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="C953" s="12"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="C954" s="12"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="C955" s="12"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="C956" s="12"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="C957" s="12"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="C958" s="12"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="C959" s="12"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="C960" s="12"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="C961" s="12"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="C962" s="12"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="C963" s="12"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="C964" s="12"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="C965" s="12"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="C966" s="12"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="C967" s="12"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="C968" s="12"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="C969" s="12"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="C970" s="12"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="C971" s="12"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="C972" s="12"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="C973" s="12"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="C974" s="12"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="C975" s="12"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="C976" s="12"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="C977" s="12"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="C978" s="12"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="C979" s="12"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="C980" s="12"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="C981" s="12"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="C982" s="12"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="C983" s="12"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="C984" s="12"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="C985" s="12"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="C986" s="12"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="C987" s="12"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="C988" s="12"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="C989" s="12"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="C990" s="12"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="C991" s="12"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="C992" s="12"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="C993" s="12"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="C994" s="12"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="C995" s="12"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="C996" s="12"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="C997" s="12"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="C998" s="12"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1">
+      <c r="C999" s="12"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="C1000" s="12"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
